--- a/resources/templates/standard/K1200-04-01.xlsx
+++ b/resources/templates/standard/K1200-04-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">타 사업부
 실적 체제 평가표</t>
@@ -846,26 +849,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1" s="4"/>
     </row>
@@ -913,12 +918,12 @@
     </row>
     <row r="5" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -931,12 +936,12 @@
     </row>
     <row r="6" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -949,34 +954,34 @@
     </row>
     <row r="7" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L7" s="3"/>
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="10">
@@ -984,7 +989,7 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -996,7 +1001,7 @@
     <row r="9" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="10">
@@ -1004,7 +1009,7 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -1015,10 +1020,10 @@
     </row>
     <row r="10" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10">
@@ -1026,7 +1031,7 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
@@ -1038,7 +1043,7 @@
     <row r="11" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="10">
@@ -1046,7 +1051,7 @@
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
@@ -1058,7 +1063,7 @@
     <row r="12" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="10">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
@@ -1077,10 +1082,10 @@
     </row>
     <row r="13" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="14">
@@ -1088,7 +1093,7 @@
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
@@ -1100,7 +1105,7 @@
     <row r="14" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="14">
@@ -1108,7 +1113,7 @@
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
@@ -1120,7 +1125,7 @@
     <row r="15" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="14">
@@ -1137,18 +1142,18 @@
     </row>
     <row r="16" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
@@ -1160,7 +1165,7 @@
     <row r="17" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="10"/>
@@ -1176,7 +1181,7 @@
     <row r="18" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="10"/>
@@ -1192,7 +1197,7 @@
     <row r="19" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
@@ -1210,7 +1215,7 @@
       <c r="B20" s="19"/>
       <c r="C20" s="20"/>
       <c r="D20" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
@@ -1223,20 +1228,20 @@
     </row>
     <row r="21" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
@@ -1246,17 +1251,17 @@
     <row r="22" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
@@ -1265,7 +1270,7 @@
     </row>
     <row r="23" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -1337,7 +1342,7 @@
     </row>
     <row r="28" ht="24.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
